--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -163,15 +163,15 @@
     <t>Urawa Reds</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
@@ -181,30 +181,30 @@
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Cuiabá</t>
   </si>
   <si>
@@ -214,15 +214,15 @@
     <t>Shonan Bellmare</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Bahia</t>
   </si>
   <si>
@@ -232,28 +232,28 @@
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
-  </si>
-  <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Internacional</t>
   </si>
   <si>
     <t>América Mineiro</t>
@@ -902,76 +902,76 @@
         <v>82</v>
       </c>
       <c r="L3">
-        <v>4.07</v>
+        <v>1.77</v>
       </c>
       <c r="M3">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N3">
-        <v>1.88</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
+        <v>1.6</v>
+      </c>
+      <c r="P3">
+        <v>9.75</v>
+      </c>
+      <c r="Q3">
         <v>2.6</v>
       </c>
-      <c r="P3">
-        <v>7.75</v>
-      </c>
-      <c r="Q3">
-        <v>1.66</v>
-      </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="T3">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="U3">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AA3">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD3">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF3">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH3">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>84</v>
@@ -1018,76 +1018,76 @@
         <v>82</v>
       </c>
       <c r="L4">
+        <v>1.77</v>
+      </c>
+      <c r="M4">
+        <v>3.23</v>
+      </c>
+      <c r="N4">
+        <v>4.1</v>
+      </c>
+      <c r="O4">
+        <v>1.68</v>
+      </c>
+      <c r="P4">
+        <v>7.75</v>
+      </c>
+      <c r="Q4">
+        <v>2.55</v>
+      </c>
+      <c r="R4">
+        <v>1.43</v>
+      </c>
+      <c r="S4">
+        <v>2.6</v>
+      </c>
+      <c r="T4">
+        <v>2.95</v>
+      </c>
+      <c r="U4">
+        <v>1.35</v>
+      </c>
+      <c r="V4">
+        <v>7.75</v>
+      </c>
+      <c r="W4">
+        <v>1.07</v>
+      </c>
+      <c r="X4">
+        <v>1.07</v>
+      </c>
+      <c r="Y4">
+        <v>8</v>
+      </c>
+      <c r="Z4">
+        <v>1.38</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <v>2.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.65</v>
+      </c>
+      <c r="AD4">
+        <v>3.8</v>
+      </c>
+      <c r="AE4">
+        <v>1.25</v>
+      </c>
+      <c r="AF4">
+        <v>1.9</v>
+      </c>
+      <c r="AG4">
         <v>1.78</v>
       </c>
-      <c r="M4">
-        <v>3.59</v>
-      </c>
-      <c r="N4">
-        <v>4.27</v>
-      </c>
-      <c r="O4">
-        <v>1.6</v>
-      </c>
-      <c r="P4">
-        <v>9.75</v>
-      </c>
-      <c r="Q4">
-        <v>2.6</v>
-      </c>
-      <c r="R4">
-        <v>1.34</v>
-      </c>
-      <c r="S4">
-        <v>2.95</v>
-      </c>
-      <c r="T4">
-        <v>2.55</v>
-      </c>
-      <c r="U4">
-        <v>1.44</v>
-      </c>
-      <c r="V4">
-        <v>6.25</v>
-      </c>
-      <c r="W4">
-        <v>1.1</v>
-      </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
-        <v>9</v>
-      </c>
-      <c r="Z4">
-        <v>1.3</v>
-      </c>
-      <c r="AA4">
-        <v>3.45</v>
-      </c>
-      <c r="AB4">
-        <v>1.94</v>
-      </c>
-      <c r="AC4">
-        <v>1.82</v>
-      </c>
-      <c r="AD4">
-        <v>3.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.33</v>
-      </c>
-      <c r="AF4">
-        <v>1.78</v>
-      </c>
-      <c r="AG4">
-        <v>1.9</v>
-      </c>
       <c r="AH4">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ4" t="s">
         <v>84</v>
@@ -1134,22 +1134,22 @@
         <v>82</v>
       </c>
       <c r="L5">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="M5">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>1.87</v>
       </c>
       <c r="O5">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="P5">
         <v>7.75</v>
       </c>
       <c r="Q5">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
         <v>1.43</v>
@@ -1161,10 +1161,10 @@
         <v>2.95</v>
       </c>
       <c r="U5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V5">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1182,10 +1182,10 @@
         <v>3</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD5">
         <v>3.8</v>
@@ -1194,10 +1194,10 @@
         <v>1.25</v>
       </c>
       <c r="AF5">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH5">
         <v>7.5</v>
@@ -1250,13 +1250,13 @@
         <v>82</v>
       </c>
       <c r="L6">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="M6">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="O6">
         <v>1.61</v>
@@ -1298,10 +1298,10 @@
         <v>3.5</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AD6">
         <v>2.9</v>
@@ -1363,16 +1363,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1479,16 +1479,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1530,10 +1530,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -1598,76 +1598,76 @@
         <v>82</v>
       </c>
       <c r="L9">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="M9">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AB9">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="s">
         <v>84</v>
@@ -1687,7 +1687,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
         <v>47</v>
@@ -1714,73 +1714,73 @@
         <v>82</v>
       </c>
       <c r="L10">
-        <v>2.66</v>
+        <v>1.8</v>
       </c>
       <c r="M10">
         <v>3.25</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O10">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S10">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="U10">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Z10">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA10">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AD10">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="AE10">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AG10">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH10">
-        <v>8.25</v>
+        <v>12.5</v>
       </c>
       <c r="AI10">
         <v>1.01</v>
@@ -1803,7 +1803,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>47</v>
@@ -1830,76 +1830,76 @@
         <v>82</v>
       </c>
       <c r="L11">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="M11">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="O11">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="U11">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V11">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y11">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z11">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AA11">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="AB11">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AC11">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AD11">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AE11">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AH11">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
         <v>84</v>
@@ -1919,7 +1919,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>47</v>
@@ -1946,76 +1946,76 @@
         <v>82</v>
       </c>
       <c r="L12">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="M12">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="N12">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z12">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA12">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="s">
         <v>84</v>
@@ -2062,13 +2062,13 @@
         <v>82</v>
       </c>
       <c r="L13">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="M13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N13">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="O13">
         <v>1.91</v>
@@ -2110,10 +2110,10 @@
         <v>2.65</v>
       </c>
       <c r="AB13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AD13">
         <v>4.55</v>
@@ -2178,76 +2178,76 @@
         <v>82</v>
       </c>
       <c r="L14">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="M14">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>3.32</v>
       </c>
       <c r="O14">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P14">
+        <v>6.75</v>
+      </c>
+      <c r="Q14">
+        <v>2.6</v>
+      </c>
+      <c r="R14">
+        <v>1.5</v>
+      </c>
+      <c r="S14">
+        <v>2.4</v>
+      </c>
+      <c r="T14">
+        <v>3.3</v>
+      </c>
+      <c r="U14">
+        <v>1.29</v>
+      </c>
+      <c r="V14">
+        <v>9</v>
+      </c>
+      <c r="W14">
+        <v>1.03</v>
+      </c>
+      <c r="X14">
+        <v>1.08</v>
+      </c>
+      <c r="Y14">
         <v>6.5</v>
       </c>
-      <c r="Q14">
-        <v>2.88</v>
-      </c>
-      <c r="R14">
-        <v>1.53</v>
-      </c>
-      <c r="S14">
-        <v>2.38</v>
-      </c>
-      <c r="T14">
-        <v>3.4</v>
-      </c>
-      <c r="U14">
-        <v>1.25</v>
-      </c>
-      <c r="V14">
-        <v>10.5</v>
-      </c>
-      <c r="W14">
-        <v>1</v>
-      </c>
-      <c r="X14">
-        <v>1.06</v>
-      </c>
-      <c r="Y14">
-        <v>7</v>
-      </c>
       <c r="Z14">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AA14">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AB14">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AD14">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH14">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AI14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="s">
         <v>84</v>
@@ -2294,13 +2294,13 @@
         <v>82</v>
       </c>
       <c r="L15">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="M15">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="N15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O15">
         <v>2.38</v>
@@ -2342,10 +2342,10 @@
         <v>2.63</v>
       </c>
       <c r="AB15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD15">
         <v>4.33</v>
@@ -2410,76 +2410,76 @@
         <v>82</v>
       </c>
       <c r="L16">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="M16">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N16">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="O16">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P16">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q16">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
+        <v>1.53</v>
+      </c>
+      <c r="S16">
+        <v>2.38</v>
+      </c>
+      <c r="T16">
+        <v>3.4</v>
+      </c>
+      <c r="U16">
+        <v>1.25</v>
+      </c>
+      <c r="V16">
+        <v>10.5</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1.06</v>
+      </c>
+      <c r="Y16">
+        <v>7</v>
+      </c>
+      <c r="Z16">
         <v>1.5</v>
       </c>
-      <c r="S16">
+      <c r="AA16">
+        <v>2.58</v>
+      </c>
+      <c r="AB16">
         <v>2.4</v>
-      </c>
-      <c r="T16">
-        <v>3.3</v>
-      </c>
-      <c r="U16">
-        <v>1.29</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>1.03</v>
-      </c>
-      <c r="X16">
-        <v>1.08</v>
-      </c>
-      <c r="Y16">
-        <v>6.5</v>
-      </c>
-      <c r="Z16">
-        <v>1.43</v>
-      </c>
-      <c r="AA16">
-        <v>2.53</v>
-      </c>
-      <c r="AB16">
-        <v>2.48</v>
       </c>
       <c r="AC16">
         <v>1.53</v>
       </c>
       <c r="AD16">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG16">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH16">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AI16">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="s">
         <v>84</v>
@@ -2574,10 +2574,10 @@
         <v>2.55</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>82</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB18">
         <v>0</v>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -145,12 +145,12 @@
     <t>21:30</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>Japan J1 League</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -160,103 +160,103 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Jeju United</t>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
   </si>
   <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>Grêmio</t>
+    <t>Novorizontino</t>
   </si>
   <si>
     <t>Ceará</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Amazonas</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Shonan Bellmare</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>FC Seoul</t>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
+    <t>Goiás</t>
   </si>
   <si>
     <t>Mirassol</t>
   </si>
   <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
     <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Sport Recife</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
   </si>
   <si>
     <t>Paysandu</t>
@@ -786,76 +786,76 @@
         <v>82</v>
       </c>
       <c r="L2">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="M2">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="P2">
+        <v>7.75</v>
+      </c>
+      <c r="Q2">
+        <v>2.55</v>
+      </c>
+      <c r="R2">
+        <v>1.43</v>
+      </c>
+      <c r="S2">
+        <v>2.6</v>
+      </c>
+      <c r="T2">
+        <v>2.95</v>
+      </c>
+      <c r="U2">
+        <v>1.35</v>
+      </c>
+      <c r="V2">
+        <v>7.75</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1.07</v>
+      </c>
+      <c r="Y2">
+        <v>8</v>
+      </c>
+      <c r="Z2">
+        <v>1.38</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>2.05</v>
+      </c>
+      <c r="AC2">
+        <v>1.65</v>
+      </c>
+      <c r="AD2">
+        <v>3.8</v>
+      </c>
+      <c r="AE2">
+        <v>1.25</v>
+      </c>
+      <c r="AF2">
+        <v>1.9</v>
+      </c>
+      <c r="AG2">
+        <v>1.78</v>
+      </c>
+      <c r="AH2">
         <v>7.5</v>
       </c>
-      <c r="Q2">
-        <v>3</v>
-      </c>
-      <c r="R2">
-        <v>1.42</v>
-      </c>
-      <c r="S2">
-        <v>2.65</v>
-      </c>
-      <c r="T2">
-        <v>2.88</v>
-      </c>
-      <c r="U2">
-        <v>1.36</v>
-      </c>
-      <c r="V2">
-        <v>8.6</v>
-      </c>
-      <c r="W2">
-        <v>1.01</v>
-      </c>
-      <c r="X2">
+      <c r="AI2">
         <v>1.08</v>
-      </c>
-      <c r="Y2">
-        <v>7.5</v>
-      </c>
-      <c r="Z2">
-        <v>1.4</v>
-      </c>
-      <c r="AA2">
-        <v>2.9</v>
-      </c>
-      <c r="AB2">
-        <v>2.01</v>
-      </c>
-      <c r="AC2">
-        <v>1.71</v>
-      </c>
-      <c r="AD2">
-        <v>4.2</v>
-      </c>
-      <c r="AE2">
-        <v>1.22</v>
-      </c>
-      <c r="AF2">
-        <v>2</v>
-      </c>
-      <c r="AG2">
-        <v>1.7</v>
-      </c>
-      <c r="AH2">
-        <v>8</v>
-      </c>
-      <c r="AI2">
-        <v>1.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>84</v>
@@ -875,7 +875,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
         <v>47</v>
@@ -902,76 +902,76 @@
         <v>82</v>
       </c>
       <c r="L3">
-        <v>1.77</v>
+        <v>3.87</v>
       </c>
       <c r="M3">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>1.83</v>
       </c>
       <c r="O3">
+        <v>2.6</v>
+      </c>
+      <c r="P3">
+        <v>7.75</v>
+      </c>
+      <c r="Q3">
+        <v>1.66</v>
+      </c>
+      <c r="R3">
+        <v>1.43</v>
+      </c>
+      <c r="S3">
+        <v>2.6</v>
+      </c>
+      <c r="T3">
+        <v>2.95</v>
+      </c>
+      <c r="U3">
+        <v>1.34</v>
+      </c>
+      <c r="V3">
+        <v>8</v>
+      </c>
+      <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
+        <v>1.07</v>
+      </c>
+      <c r="Y3">
+        <v>8</v>
+      </c>
+      <c r="Z3">
+        <v>1.38</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
+        <v>2.1</v>
+      </c>
+      <c r="AC3">
         <v>1.6</v>
       </c>
-      <c r="P3">
-        <v>9.75</v>
-      </c>
-      <c r="Q3">
-        <v>2.6</v>
-      </c>
-      <c r="R3">
-        <v>1.34</v>
-      </c>
-      <c r="S3">
-        <v>2.95</v>
-      </c>
-      <c r="T3">
-        <v>2.55</v>
-      </c>
-      <c r="U3">
-        <v>1.44</v>
-      </c>
-      <c r="V3">
-        <v>6.25</v>
-      </c>
-      <c r="W3">
-        <v>1.1</v>
-      </c>
-      <c r="X3">
-        <v>1.05</v>
-      </c>
-      <c r="Y3">
-        <v>9</v>
-      </c>
-      <c r="Z3">
-        <v>1.3</v>
-      </c>
-      <c r="AA3">
-        <v>3.45</v>
-      </c>
-      <c r="AB3">
-        <v>1.8</v>
-      </c>
-      <c r="AC3">
-        <v>1.83</v>
-      </c>
       <c r="AD3">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AE3">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AG3">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AH3">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ3" t="s">
         <v>84</v>
@@ -1018,76 +1018,76 @@
         <v>82</v>
       </c>
       <c r="L4">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="M4">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="P4">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q4">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T4">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V4">
-        <v>7.75</v>
+        <v>8.6</v>
       </c>
       <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
+        <v>1.08</v>
+      </c>
+      <c r="Y4">
+        <v>7.5</v>
+      </c>
+      <c r="Z4">
+        <v>1.4</v>
+      </c>
+      <c r="AA4">
+        <v>2.9</v>
+      </c>
+      <c r="AB4">
+        <v>2.01</v>
+      </c>
+      <c r="AC4">
+        <v>1.71</v>
+      </c>
+      <c r="AD4">
+        <v>4.2</v>
+      </c>
+      <c r="AE4">
+        <v>1.22</v>
+      </c>
+      <c r="AF4">
+        <v>2</v>
+      </c>
+      <c r="AG4">
+        <v>1.7</v>
+      </c>
+      <c r="AH4">
+        <v>8</v>
+      </c>
+      <c r="AI4">
         <v>1.07</v>
-      </c>
-      <c r="X4">
-        <v>1.07</v>
-      </c>
-      <c r="Y4">
-        <v>8</v>
-      </c>
-      <c r="Z4">
-        <v>1.38</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
-      <c r="AB4">
-        <v>2.05</v>
-      </c>
-      <c r="AC4">
-        <v>1.65</v>
-      </c>
-      <c r="AD4">
-        <v>3.8</v>
-      </c>
-      <c r="AE4">
-        <v>1.25</v>
-      </c>
-      <c r="AF4">
-        <v>1.9</v>
-      </c>
-      <c r="AG4">
-        <v>1.78</v>
-      </c>
-      <c r="AH4">
-        <v>7.5</v>
-      </c>
-      <c r="AI4">
-        <v>1.08</v>
       </c>
       <c r="AJ4" t="s">
         <v>84</v>
@@ -1107,7 +1107,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>47</v>
@@ -1134,76 +1134,76 @@
         <v>82</v>
       </c>
       <c r="L5">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="M5">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>1.6</v>
+      </c>
+      <c r="P5">
+        <v>9.75</v>
+      </c>
+      <c r="Q5">
+        <v>2.6</v>
+      </c>
+      <c r="R5">
+        <v>1.34</v>
+      </c>
+      <c r="S5">
+        <v>2.95</v>
+      </c>
+      <c r="T5">
+        <v>2.55</v>
+      </c>
+      <c r="U5">
+        <v>1.44</v>
+      </c>
+      <c r="V5">
+        <v>6.25</v>
+      </c>
+      <c r="W5">
+        <v>1.1</v>
+      </c>
+      <c r="X5">
+        <v>1.05</v>
+      </c>
+      <c r="Y5">
+        <v>9</v>
+      </c>
+      <c r="Z5">
+        <v>1.3</v>
+      </c>
+      <c r="AA5">
+        <v>3.45</v>
+      </c>
+      <c r="AB5">
         <v>1.87</v>
       </c>
-      <c r="O5">
-        <v>2.6</v>
-      </c>
-      <c r="P5">
-        <v>7.75</v>
-      </c>
-      <c r="Q5">
-        <v>1.66</v>
-      </c>
-      <c r="R5">
-        <v>1.43</v>
-      </c>
-      <c r="S5">
-        <v>2.6</v>
-      </c>
-      <c r="T5">
-        <v>2.95</v>
-      </c>
-      <c r="U5">
-        <v>1.34</v>
-      </c>
-      <c r="V5">
-        <v>8</v>
-      </c>
-      <c r="W5">
-        <v>1.07</v>
-      </c>
-      <c r="X5">
-        <v>1.07</v>
-      </c>
-      <c r="Y5">
-        <v>8</v>
-      </c>
-      <c r="Z5">
-        <v>1.38</v>
-      </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>2.1</v>
-      </c>
       <c r="AC5">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AD5">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AE5">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH5">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI5">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
         <v>84</v>
@@ -1247,79 +1247,79 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L6">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="M6">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N6">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AC6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AD6">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>84</v>
@@ -1366,13 +1366,13 @@
         <v>83</v>
       </c>
       <c r="L7">
-        <v>1.72</v>
+        <v>2.89</v>
       </c>
       <c r="M7">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>2.51</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1479,79 +1479,79 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="M8">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N8">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="s">
         <v>84</v>
@@ -1571,7 +1571,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -1598,76 +1598,76 @@
         <v>82</v>
       </c>
       <c r="L9">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="M9">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="N9">
-        <v>3.53</v>
+        <v>3.74</v>
       </c>
       <c r="O9">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="R9">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T9">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="U9">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V9">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="Z9">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AA9">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="AC9">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AD9">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AG9">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
         <v>84</v>
@@ -1687,7 +1687,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>47</v>
@@ -1714,76 +1714,76 @@
         <v>82</v>
       </c>
       <c r="L10">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="M10">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N10">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
         <v>2.4</v>
       </c>
       <c r="T10">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
         <v>1.04</v>
       </c>
-      <c r="X10">
-        <v>1.06</v>
-      </c>
       <c r="Y10">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z10">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA10">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="AB10">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD10">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AH10">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="s">
         <v>84</v>
@@ -1803,7 +1803,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>47</v>
@@ -1830,73 +1830,73 @@
         <v>82</v>
       </c>
       <c r="L11">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="M11">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="N11">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="S11">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="T11">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y11">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z11">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AA11">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB11">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC11">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF11">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AH11">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AI11">
         <v>1.03</v>
@@ -1919,7 +1919,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>47</v>
@@ -1946,76 +1946,76 @@
         <v>82</v>
       </c>
       <c r="L12">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="M12">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N12">
-        <v>2.66</v>
+        <v>3.87</v>
       </c>
       <c r="O12">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="S12">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="U12">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y12">
-        <v>7.1</v>
+        <v>5.75</v>
       </c>
       <c r="Z12">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA12">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC12">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AD12">
-        <v>4.3</v>
+        <v>5.75</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AG12">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AH12">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="AI12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ12" t="s">
         <v>84</v>
@@ -2080,31 +2080,31 @@
         <v>2.25</v>
       </c>
       <c r="R13">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="S13">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="T13">
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z13">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AA13">
         <v>2.65</v>
@@ -2116,22 +2116,22 @@
         <v>1.55</v>
       </c>
       <c r="AD13">
-        <v>4.55</v>
+        <v>4.85</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF13">
         <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI13">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="s">
         <v>84</v>
@@ -2151,7 +2151,7 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -2178,76 +2178,76 @@
         <v>82</v>
       </c>
       <c r="L14">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="M14">
-        <v>3.09</v>
+        <v>2.79</v>
       </c>
       <c r="N14">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="O14">
         <v>1.67</v>
       </c>
       <c r="P14">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S14">
         <v>2.4</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="U14">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y14">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="Z14">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AA14">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC14">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AD14">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AE14">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AG14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH14">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AI14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="s">
         <v>84</v>
@@ -2294,73 +2294,73 @@
         <v>82</v>
       </c>
       <c r="L15">
-        <v>2.93</v>
+        <v>2.02</v>
       </c>
       <c r="M15">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="N15">
-        <v>2.24</v>
+        <v>3.32</v>
       </c>
       <c r="O15">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="P15">
         <v>6.75</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S15">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U15">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V15">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>6.85</v>
+        <v>6.25</v>
       </c>
       <c r="Z15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AA15">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC15">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD15">
         <v>4.33</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AH15">
-        <v>8.75</v>
+        <v>8.6</v>
       </c>
       <c r="AI15">
         <v>1.02</v>
@@ -2431,31 +2431,31 @@
         <v>1.53</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T16">
         <v>3.4</v>
       </c>
       <c r="U16">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>1.5</v>
       </c>
       <c r="AA16">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="AB16">
         <v>2.4</v>
@@ -2464,22 +2464,22 @@
         <v>1.53</v>
       </c>
       <c r="AD16">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AE16">
         <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AH16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI16">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="s">
         <v>84</v>
@@ -2499,7 +2499,7 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
         <v>47</v>
@@ -2526,76 +2526,76 @@
         <v>82</v>
       </c>
       <c r="L17">
-        <v>2.03</v>
+        <v>2.93</v>
       </c>
       <c r="M17">
+        <v>3.02</v>
+      </c>
+      <c r="N17">
+        <v>2.24</v>
+      </c>
+      <c r="O17">
+        <v>2.38</v>
+      </c>
+      <c r="P17">
+        <v>6.75</v>
+      </c>
+      <c r="Q17">
+        <v>1.8</v>
+      </c>
+      <c r="R17">
+        <v>1.48</v>
+      </c>
+      <c r="S17">
+        <v>2.45</v>
+      </c>
+      <c r="T17">
         <v>3.2</v>
       </c>
-      <c r="N17">
-        <v>3.7</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z17">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AA17">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB17">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ17" t="s">
         <v>84</v>
@@ -2642,46 +2642,46 @@
         <v>82</v>
       </c>
       <c r="L18">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="M18">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z18">
         <v>1.48</v>
@@ -2690,28 +2690,28 @@
         <v>2.37</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ18" t="s">
         <v>84</v>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="93">
   <si>
     <t>Date</t>
   </si>
@@ -136,6 +136,12 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -154,21 +160,27 @@
     <t>Brazil Serie A</t>
   </si>
   <si>
+    <t>Europe UEFA Champions League</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Urawa Reds</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Urawa Reds</t>
-  </si>
-  <si>
     <t>Ulsan</t>
   </si>
   <si>
@@ -181,45 +193,51 @@
     <t>Vasco da Gama</t>
   </si>
   <si>
+    <t>Brann</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Chapecoense</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Santos</t>
+    <t>Bragantino</t>
   </si>
   <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Shonan Bellmare</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
@@ -232,34 +250,40 @@
     <t>Bahia</t>
   </si>
   <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Internacional</t>
+    <t>Flamengo</t>
   </si>
   <si>
     <t>Sport Recife</t>
-  </si>
-  <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -632,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AL20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -759,16 +783,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -783,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L2">
         <v>1.77</v>
@@ -834,10 +858,10 @@
         <v>3</v>
       </c>
       <c r="AB2">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AD2">
         <v>3.8</v>
@@ -858,10 +882,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL2" s="3">
         <v>45861.3125</v>
@@ -875,16 +899,16 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -899,85 +923,85 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L3">
-        <v>3.87</v>
+        <v>1.91</v>
       </c>
       <c r="M3">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="N3">
-        <v>1.83</v>
+        <v>3.45</v>
       </c>
       <c r="O3">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T3">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V3">
+        <v>8.6</v>
+      </c>
+      <c r="W3">
+        <v>1.01</v>
+      </c>
+      <c r="X3">
+        <v>1.08</v>
+      </c>
+      <c r="Y3">
+        <v>7.5</v>
+      </c>
+      <c r="Z3">
+        <v>1.4</v>
+      </c>
+      <c r="AA3">
+        <v>2.9</v>
+      </c>
+      <c r="AB3">
+        <v>2.01</v>
+      </c>
+      <c r="AC3">
+        <v>1.71</v>
+      </c>
+      <c r="AD3">
+        <v>4.2</v>
+      </c>
+      <c r="AE3">
+        <v>1.22</v>
+      </c>
+      <c r="AF3">
+        <v>2</v>
+      </c>
+      <c r="AG3">
+        <v>1.7</v>
+      </c>
+      <c r="AH3">
         <v>8</v>
       </c>
-      <c r="W3">
+      <c r="AI3">
         <v>1.07</v>
       </c>
-      <c r="X3">
-        <v>1.07</v>
-      </c>
-      <c r="Y3">
-        <v>8</v>
-      </c>
-      <c r="Z3">
-        <v>1.38</v>
-      </c>
-      <c r="AA3">
-        <v>3</v>
-      </c>
-      <c r="AB3">
-        <v>2.1</v>
-      </c>
-      <c r="AC3">
-        <v>1.6</v>
-      </c>
-      <c r="AD3">
-        <v>3.8</v>
-      </c>
-      <c r="AE3">
-        <v>1.25</v>
-      </c>
-      <c r="AF3">
-        <v>1.93</v>
-      </c>
-      <c r="AG3">
-        <v>1.75</v>
-      </c>
-      <c r="AH3">
-        <v>7.5</v>
-      </c>
-      <c r="AI3">
-        <v>1.08</v>
-      </c>
       <c r="AJ3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL3" s="3">
         <v>45861.3125</v>
@@ -991,16 +1015,16 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1015,85 +1039,85 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L4">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="M4">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="O4">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="P4">
+        <v>7.75</v>
+      </c>
+      <c r="Q4">
+        <v>1.66</v>
+      </c>
+      <c r="R4">
+        <v>1.43</v>
+      </c>
+      <c r="S4">
+        <v>2.6</v>
+      </c>
+      <c r="T4">
+        <v>2.95</v>
+      </c>
+      <c r="U4">
+        <v>1.34</v>
+      </c>
+      <c r="V4">
+        <v>8</v>
+      </c>
+      <c r="W4">
+        <v>1.07</v>
+      </c>
+      <c r="X4">
+        <v>1.07</v>
+      </c>
+      <c r="Y4">
+        <v>8</v>
+      </c>
+      <c r="Z4">
+        <v>1.38</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <v>1.93</v>
+      </c>
+      <c r="AC4">
+        <v>1.77</v>
+      </c>
+      <c r="AD4">
+        <v>3.8</v>
+      </c>
+      <c r="AE4">
+        <v>1.25</v>
+      </c>
+      <c r="AF4">
+        <v>1.93</v>
+      </c>
+      <c r="AG4">
+        <v>1.75</v>
+      </c>
+      <c r="AH4">
         <v>7.5</v>
       </c>
-      <c r="Q4">
-        <v>3</v>
-      </c>
-      <c r="R4">
-        <v>1.42</v>
-      </c>
-      <c r="S4">
-        <v>2.65</v>
-      </c>
-      <c r="T4">
-        <v>2.88</v>
-      </c>
-      <c r="U4">
-        <v>1.36</v>
-      </c>
-      <c r="V4">
-        <v>8.6</v>
-      </c>
-      <c r="W4">
-        <v>1.01</v>
-      </c>
-      <c r="X4">
+      <c r="AI4">
         <v>1.08</v>
       </c>
-      <c r="Y4">
-        <v>7.5</v>
-      </c>
-      <c r="Z4">
-        <v>1.4</v>
-      </c>
-      <c r="AA4">
-        <v>2.9</v>
-      </c>
-      <c r="AB4">
-        <v>2.01</v>
-      </c>
-      <c r="AC4">
-        <v>1.71</v>
-      </c>
-      <c r="AD4">
-        <v>4.2</v>
-      </c>
-      <c r="AE4">
-        <v>1.22</v>
-      </c>
-      <c r="AF4">
-        <v>2</v>
-      </c>
-      <c r="AG4">
-        <v>1.7</v>
-      </c>
-      <c r="AH4">
-        <v>8</v>
-      </c>
-      <c r="AI4">
-        <v>1.07</v>
-      </c>
       <c r="AJ4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL4" s="3">
         <v>45861.3125</v>
@@ -1107,16 +1131,16 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1131,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L5">
         <v>1.73</v>
@@ -1206,10 +1230,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL5" s="3">
         <v>45861.3125</v>
@@ -1223,16 +1247,16 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1247,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L6">
         <v>1.72</v>
@@ -1322,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL6" s="3">
         <v>45861.5</v>
@@ -1339,16 +1363,16 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1363,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L7">
         <v>2.89</v>
@@ -1438,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK7" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL7" s="3">
         <v>45861.5</v>
@@ -1455,16 +1479,16 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1479,16 +1503,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L8">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="M8">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="N8">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="O8">
         <v>1.61</v>
@@ -1554,10 +1578,10 @@
         <v>1.13</v>
       </c>
       <c r="AJ8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL8" s="3">
         <v>45861.5</v>
@@ -1571,16 +1595,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1595,88 +1619,88 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L9">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="M9">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="N9">
-        <v>3.74</v>
+        <v>1.94</v>
       </c>
       <c r="O9">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="P9">
-        <v>5.25</v>
+        <v>12</v>
       </c>
       <c r="Q9">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="T9">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="U9">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="V9">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB9">
-        <v>2.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC9">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>2.88</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AF9">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AH9">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AI9">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL9" s="3">
-        <v>45861.79166666666</v>
+        <v>45861.58333333334</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1684,19 +1708,19 @@
         <v>45861</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1711,88 +1735,88 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L10">
-        <v>2.01</v>
+        <v>4.9</v>
       </c>
       <c r="M10">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="N10">
-        <v>3.53</v>
+        <v>1.55</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="R10">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="V10">
-        <v>8.699999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
         <v>1.01</v>
       </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
       <c r="Y10">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AA10">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="AB10">
+        <v>1.75</v>
+      </c>
+      <c r="AC10">
+        <v>1.95</v>
+      </c>
+      <c r="AD10">
         <v>2.2</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <v>1.61</v>
       </c>
-      <c r="AD10">
-        <v>4.6</v>
-      </c>
-      <c r="AE10">
-        <v>1.18</v>
-      </c>
       <c r="AF10">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AG10">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AH10">
-        <v>8.4</v>
+        <v>5.15</v>
       </c>
       <c r="AI10">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AJ10" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK10" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL10" s="3">
-        <v>45861.79166666666</v>
+        <v>45861.65625</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -1800,19 +1824,19 @@
         <v>45861</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1827,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L11">
         <v>2.48</v>
@@ -1848,28 +1872,28 @@
         <v>2.2</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z11">
         <v>1.42</v>
@@ -1878,34 +1902,34 @@
         <v>2.8</v>
       </c>
       <c r="AB11">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC11">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AD11">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AE11">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
         <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AH11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AI11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL11" s="3">
         <v>45861.79166666666</v>
@@ -1916,19 +1940,19 @@
         <v>45861</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1943,37 +1967,37 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L12">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="M12">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="N12">
-        <v>3.87</v>
+        <v>3.74</v>
       </c>
       <c r="O12">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="P12">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R12">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S12">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="T12">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V12">
         <v>11.5</v>
@@ -1982,46 +2006,46 @@
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y12">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="Z12">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA12">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB12">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="AC12">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AD12">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK12" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL12" s="3">
         <v>45861.79166666666</v>
@@ -2032,19 +2056,19 @@
         <v>45861</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2059,88 +2083,88 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L13">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="M13">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="N13">
-        <v>2.67</v>
+        <v>3.53</v>
       </c>
       <c r="O13">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R13">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S13">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V13">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W13">
+        <v>1.04</v>
+      </c>
+      <c r="X13">
+        <v>1.1</v>
+      </c>
+      <c r="Y13">
+        <v>6.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.44</v>
+      </c>
+      <c r="AA13">
+        <v>2.6</v>
+      </c>
+      <c r="AB13">
+        <v>2.6</v>
+      </c>
+      <c r="AC13">
+        <v>1.43</v>
+      </c>
+      <c r="AD13">
+        <v>4.65</v>
+      </c>
+      <c r="AE13">
+        <v>1.14</v>
+      </c>
+      <c r="AF13">
+        <v>2.1</v>
+      </c>
+      <c r="AG13">
+        <v>1.67</v>
+      </c>
+      <c r="AH13">
         <v>9</v>
       </c>
-      <c r="W13">
-        <v>1</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>6.55</v>
-      </c>
-      <c r="Z13">
-        <v>1.45</v>
-      </c>
-      <c r="AA13">
-        <v>2.65</v>
-      </c>
-      <c r="AB13">
-        <v>2.3</v>
-      </c>
-      <c r="AC13">
-        <v>1.55</v>
-      </c>
-      <c r="AD13">
-        <v>4.85</v>
-      </c>
-      <c r="AE13">
-        <v>1.12</v>
-      </c>
-      <c r="AF13">
-        <v>2</v>
-      </c>
-      <c r="AG13">
-        <v>1.7</v>
-      </c>
-      <c r="AH13">
-        <v>10</v>
-      </c>
       <c r="AI13">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK13" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL13" s="3">
-        <v>45861.8125</v>
+        <v>45861.79166666666</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2151,16 +2175,16 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2175,88 +2199,88 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L14">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="M14">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="N14">
-        <v>3.53</v>
+        <v>3.87</v>
       </c>
       <c r="O14">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P14">
         <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="S14">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="T14">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="U14">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="V14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="Z14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AA14">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AB14">
-        <v>2.37</v>
+        <v>2.81</v>
       </c>
       <c r="AC14">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AD14">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AG14">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AH14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK14" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL14" s="3">
-        <v>45861.89583333334</v>
+        <v>45861.79166666666</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2264,19 +2288,19 @@
         <v>45861</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2291,88 +2315,88 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L15">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="M15">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="N15">
-        <v>3.32</v>
+        <v>2.67</v>
       </c>
       <c r="O15">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="P15">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S15">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="T15">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V15">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y15">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="Z15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA15">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AB15">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC15">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AD15">
-        <v>4.33</v>
+        <v>5.15</v>
       </c>
       <c r="AE15">
         <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AG15">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AH15">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AI15">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK15" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL15" s="3">
-        <v>45861.89583333334</v>
+        <v>45861.8125</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2380,19 +2404,19 @@
         <v>45861</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2407,31 +2431,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L16">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="M16">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="N16">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="O16">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P16">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S16">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="T16">
         <v>3.4</v>
@@ -2440,34 +2464,34 @@
         <v>1.29</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
         <v>1.05</v>
       </c>
-      <c r="X16">
-        <v>1.11</v>
-      </c>
       <c r="Y16">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z16">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA16">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB16">
         <v>2.4</v>
       </c>
       <c r="AC16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD16">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
         <v>2.1</v>
@@ -2476,16 +2500,16 @@
         <v>1.7</v>
       </c>
       <c r="AH16">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI16">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK16" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL16" s="3">
         <v>45861.89583333334</v>
@@ -2496,19 +2520,19 @@
         <v>45861</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2523,85 +2547,85 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L17">
-        <v>2.93</v>
+        <v>2.02</v>
       </c>
       <c r="M17">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="N17">
-        <v>2.24</v>
+        <v>3.32</v>
       </c>
       <c r="O17">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="P17">
         <v>6.75</v>
       </c>
       <c r="Q17">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S17">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1.1</v>
+      </c>
+      <c r="Y17">
+        <v>6.5</v>
+      </c>
+      <c r="Z17">
+        <v>1.44</v>
+      </c>
+      <c r="AA17">
+        <v>2.5</v>
+      </c>
+      <c r="AB17">
+        <v>2.48</v>
+      </c>
+      <c r="AC17">
+        <v>1.47</v>
+      </c>
+      <c r="AD17">
+        <v>4.8</v>
+      </c>
+      <c r="AE17">
+        <v>1.17</v>
+      </c>
+      <c r="AF17">
+        <v>2.03</v>
+      </c>
+      <c r="AG17">
+        <v>1.72</v>
+      </c>
+      <c r="AH17">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AI17">
         <v>1.05</v>
       </c>
-      <c r="X17">
-        <v>1.04</v>
-      </c>
-      <c r="Y17">
-        <v>7.5</v>
-      </c>
-      <c r="Z17">
-        <v>1.38</v>
-      </c>
-      <c r="AA17">
-        <v>2.6</v>
-      </c>
-      <c r="AB17">
-        <v>2.2</v>
-      </c>
-      <c r="AC17">
-        <v>1.6</v>
-      </c>
-      <c r="AD17">
-        <v>4.2</v>
-      </c>
-      <c r="AE17">
-        <v>1.18</v>
-      </c>
-      <c r="AF17">
-        <v>1.95</v>
-      </c>
-      <c r="AG17">
-        <v>1.75</v>
-      </c>
-      <c r="AH17">
-        <v>8.75</v>
-      </c>
-      <c r="AI17">
-        <v>1.06</v>
-      </c>
       <c r="AJ17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AL17" s="3">
         <v>45861.89583333334</v>
@@ -2612,19 +2636,19 @@
         <v>45861</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2639,87 +2663,319 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L18">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="M18">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="N18">
         <v>3.53</v>
       </c>
       <c r="O18">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P18">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q18">
         <v>2.75</v>
       </c>
       <c r="R18">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="U18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
         <v>1.11</v>
       </c>
       <c r="Y18">
+        <v>6.36</v>
+      </c>
+      <c r="Z18">
+        <v>1.49</v>
+      </c>
+      <c r="AA18">
+        <v>2.55</v>
+      </c>
+      <c r="AB18">
+        <v>2.37</v>
+      </c>
+      <c r="AC18">
+        <v>1.48</v>
+      </c>
+      <c r="AD18">
+        <v>4.8</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>2.15</v>
+      </c>
+      <c r="AG18">
+        <v>1.63</v>
+      </c>
+      <c r="AH18">
+        <v>12</v>
+      </c>
+      <c r="AI18">
+        <v>1.01</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>45861.89583333334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" s="2">
+        <v>45861</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19">
+        <v>2.93</v>
+      </c>
+      <c r="M19">
+        <v>3.02</v>
+      </c>
+      <c r="N19">
+        <v>2.24</v>
+      </c>
+      <c r="O19">
+        <v>2.38</v>
+      </c>
+      <c r="P19">
+        <v>6.75</v>
+      </c>
+      <c r="Q19">
+        <v>1.8</v>
+      </c>
+      <c r="R19">
+        <v>1.46</v>
+      </c>
+      <c r="S19">
+        <v>2.55</v>
+      </c>
+      <c r="T19">
+        <v>3.18</v>
+      </c>
+      <c r="U19">
+        <v>1.28</v>
+      </c>
+      <c r="V19">
+        <v>7.5</v>
+      </c>
+      <c r="W19">
+        <v>1.05</v>
+      </c>
+      <c r="X19">
+        <v>1.07</v>
+      </c>
+      <c r="Y19">
+        <v>7</v>
+      </c>
+      <c r="Z19">
+        <v>1.42</v>
+      </c>
+      <c r="AA19">
+        <v>2.62</v>
+      </c>
+      <c r="AB19">
+        <v>2.29</v>
+      </c>
+      <c r="AC19">
+        <v>1.55</v>
+      </c>
+      <c r="AD19">
+        <v>4.2</v>
+      </c>
+      <c r="AE19">
+        <v>1.2</v>
+      </c>
+      <c r="AF19">
+        <v>2.06</v>
+      </c>
+      <c r="AG19">
+        <v>1.73</v>
+      </c>
+      <c r="AH19">
+        <v>7.9</v>
+      </c>
+      <c r="AI19">
+        <v>1.02</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL19" s="3">
+        <v>45861.89583333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38">
+      <c r="A20" s="2">
+        <v>45861</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20">
+        <v>1.84</v>
+      </c>
+      <c r="M20">
+        <v>3.08</v>
+      </c>
+      <c r="N20">
+        <v>3.96</v>
+      </c>
+      <c r="O20">
+        <v>1.62</v>
+      </c>
+      <c r="P20">
         <v>6.5</v>
       </c>
-      <c r="Z18">
-        <v>1.48</v>
-      </c>
-      <c r="AA18">
-        <v>2.37</v>
-      </c>
-      <c r="AB18">
-        <v>2.4</v>
-      </c>
-      <c r="AC18">
-        <v>1.52</v>
-      </c>
-      <c r="AD18">
-        <v>4.85</v>
-      </c>
-      <c r="AE18">
+      <c r="Q20">
+        <v>2.88</v>
+      </c>
+      <c r="R20">
+        <v>1.55</v>
+      </c>
+      <c r="S20">
+        <v>2.3</v>
+      </c>
+      <c r="T20">
+        <v>3.48</v>
+      </c>
+      <c r="U20">
+        <v>1.24</v>
+      </c>
+      <c r="V20">
+        <v>11</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.09</v>
+      </c>
+      <c r="Y20">
+        <v>6.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.53</v>
+      </c>
+      <c r="AA20">
+        <v>2.58</v>
+      </c>
+      <c r="AB20">
+        <v>2.65</v>
+      </c>
+      <c r="AC20">
+        <v>1.41</v>
+      </c>
+      <c r="AD20">
+        <v>4.75</v>
+      </c>
+      <c r="AE20">
         <v>1.15</v>
       </c>
-      <c r="AF18">
-        <v>2.1</v>
-      </c>
-      <c r="AG18">
-        <v>1.67</v>
-      </c>
-      <c r="AH18">
-        <v>11</v>
-      </c>
-      <c r="AI18">
-        <v>1.05</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AF20">
+        <v>2.2</v>
+      </c>
+      <c r="AG20">
+        <v>1.64</v>
+      </c>
+      <c r="AH20">
+        <v>12</v>
+      </c>
+      <c r="AI20">
+        <v>1.04</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45861.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -172,27 +172,27 @@
     <t>2025/2026</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
   </si>
   <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>Brann</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Fluminense</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>Chapecoense</t>
   </si>
   <si>
@@ -217,39 +217,39 @@
     <t>Amazonas</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Vitória</t>
+    <t>FC Seoul</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Shonan Bellmare</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
   </si>
   <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
     <t>Salzburg</t>
   </si>
   <si>
@@ -259,12 +259,12 @@
     <t>Palmeiras</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
@@ -274,16 +274,16 @@
     <t>Paysandu</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
     <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Sport Recife</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -810,22 +810,22 @@
         <v>90</v>
       </c>
       <c r="L2">
-        <v>1.77</v>
+        <v>3.87</v>
       </c>
       <c r="M2">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>1.83</v>
       </c>
       <c r="O2">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="P2">
         <v>7.75</v>
       </c>
       <c r="Q2">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="R2">
         <v>1.43</v>
@@ -837,10 +837,10 @@
         <v>2.95</v>
       </c>
       <c r="U2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V2">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -858,10 +858,10 @@
         <v>3</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AD2">
         <v>3.8</v>
@@ -870,10 +870,10 @@
         <v>1.25</v>
       </c>
       <c r="AF2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH2">
         <v>7.5</v>
@@ -899,7 +899,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -926,76 +926,76 @@
         <v>90</v>
       </c>
       <c r="L3">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="M3">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="N3">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="P3">
+        <v>7.75</v>
+      </c>
+      <c r="Q3">
+        <v>2.55</v>
+      </c>
+      <c r="R3">
+        <v>1.43</v>
+      </c>
+      <c r="S3">
+        <v>2.6</v>
+      </c>
+      <c r="T3">
+        <v>2.95</v>
+      </c>
+      <c r="U3">
+        <v>1.35</v>
+      </c>
+      <c r="V3">
+        <v>7.75</v>
+      </c>
+      <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
+        <v>1.07</v>
+      </c>
+      <c r="Y3">
+        <v>8</v>
+      </c>
+      <c r="Z3">
+        <v>1.38</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
+        <v>1.95</v>
+      </c>
+      <c r="AC3">
+        <v>1.75</v>
+      </c>
+      <c r="AD3">
+        <v>3.8</v>
+      </c>
+      <c r="AE3">
+        <v>1.25</v>
+      </c>
+      <c r="AF3">
+        <v>1.9</v>
+      </c>
+      <c r="AG3">
+        <v>1.78</v>
+      </c>
+      <c r="AH3">
         <v>7.5</v>
       </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-      <c r="R3">
-        <v>1.42</v>
-      </c>
-      <c r="S3">
-        <v>2.65</v>
-      </c>
-      <c r="T3">
-        <v>2.88</v>
-      </c>
-      <c r="U3">
-        <v>1.36</v>
-      </c>
-      <c r="V3">
-        <v>8.6</v>
-      </c>
-      <c r="W3">
-        <v>1.01</v>
-      </c>
-      <c r="X3">
+      <c r="AI3">
         <v>1.08</v>
-      </c>
-      <c r="Y3">
-        <v>7.5</v>
-      </c>
-      <c r="Z3">
-        <v>1.4</v>
-      </c>
-      <c r="AA3">
-        <v>2.9</v>
-      </c>
-      <c r="AB3">
-        <v>2.01</v>
-      </c>
-      <c r="AC3">
-        <v>1.71</v>
-      </c>
-      <c r="AD3">
-        <v>4.2</v>
-      </c>
-      <c r="AE3">
-        <v>1.22</v>
-      </c>
-      <c r="AF3">
-        <v>2</v>
-      </c>
-      <c r="AG3">
-        <v>1.7</v>
-      </c>
-      <c r="AH3">
-        <v>8</v>
-      </c>
-      <c r="AI3">
-        <v>1.07</v>
       </c>
       <c r="AJ3" t="s">
         <v>92</v>
@@ -1042,76 +1042,76 @@
         <v>90</v>
       </c>
       <c r="L4">
-        <v>3.87</v>
+        <v>1.73</v>
       </c>
       <c r="M4">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>1.6</v>
+      </c>
+      <c r="P4">
+        <v>9.75</v>
+      </c>
+      <c r="Q4">
+        <v>2.6</v>
+      </c>
+      <c r="R4">
+        <v>1.34</v>
+      </c>
+      <c r="S4">
+        <v>2.95</v>
+      </c>
+      <c r="T4">
+        <v>2.55</v>
+      </c>
+      <c r="U4">
+        <v>1.44</v>
+      </c>
+      <c r="V4">
+        <v>6.25</v>
+      </c>
+      <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>9</v>
+      </c>
+      <c r="Z4">
+        <v>1.3</v>
+      </c>
+      <c r="AA4">
+        <v>3.45</v>
+      </c>
+      <c r="AB4">
+        <v>1.87</v>
+      </c>
+      <c r="AC4">
         <v>1.83</v>
       </c>
-      <c r="O4">
-        <v>2.6</v>
-      </c>
-      <c r="P4">
-        <v>7.75</v>
-      </c>
-      <c r="Q4">
-        <v>1.66</v>
-      </c>
-      <c r="R4">
-        <v>1.43</v>
-      </c>
-      <c r="S4">
-        <v>2.6</v>
-      </c>
-      <c r="T4">
-        <v>2.95</v>
-      </c>
-      <c r="U4">
-        <v>1.34</v>
-      </c>
-      <c r="V4">
-        <v>8</v>
-      </c>
-      <c r="W4">
-        <v>1.07</v>
-      </c>
-      <c r="X4">
-        <v>1.07</v>
-      </c>
-      <c r="Y4">
-        <v>8</v>
-      </c>
-      <c r="Z4">
-        <v>1.38</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
-      <c r="AB4">
-        <v>1.93</v>
-      </c>
-      <c r="AC4">
-        <v>1.77</v>
-      </c>
       <c r="AD4">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AE4">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH4">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>92</v>
@@ -1131,7 +1131,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
@@ -1158,76 +1158,76 @@
         <v>90</v>
       </c>
       <c r="L5">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="M5">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P5">
-        <v>9.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S5">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="T5">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V5">
-        <v>6.25</v>
+        <v>8.6</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Z5">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AA5">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="AB5">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AD5">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH5">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AI5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AJ5" t="s">
         <v>92</v>
@@ -1274,76 +1274,76 @@
         <v>91</v>
       </c>
       <c r="L6">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB6">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="s">
         <v>92</v>
@@ -1390,13 +1390,13 @@
         <v>91</v>
       </c>
       <c r="L7">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="M7">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N7">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1506,76 +1506,76 @@
         <v>91</v>
       </c>
       <c r="L8">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="M8">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="N8">
-        <v>2.66</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AC8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AD8">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
         <v>92</v>
@@ -1854,13 +1854,13 @@
         <v>90</v>
       </c>
       <c r="L11">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="M11">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="N11">
-        <v>2.66</v>
+        <v>2.31</v>
       </c>
       <c r="O11">
         <v>1.91</v>
@@ -1872,16 +1872,16 @@
         <v>2.2</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T11">
         <v>3.5</v>
       </c>
       <c r="U11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1893,37 +1893,37 @@
         <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
       <c r="Z11">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="AB11">
         <v>2.6</v>
       </c>
       <c r="AC11">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AD11">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
         <v>1.73</v>
       </c>
       <c r="AH11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AI11">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="s">
         <v>92</v>
@@ -1943,7 +1943,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
@@ -1970,76 +1970,76 @@
         <v>90</v>
       </c>
       <c r="L12">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="M12">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="N12">
-        <v>3.74</v>
+        <v>3.06</v>
       </c>
       <c r="O12">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="P12">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S12">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="T12">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U12">
+        <v>1.29</v>
+      </c>
+      <c r="V12">
+        <v>9.5</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.04</v>
+      </c>
+      <c r="Y12">
+        <v>7.27</v>
+      </c>
+      <c r="Z12">
+        <v>1.44</v>
+      </c>
+      <c r="AA12">
+        <v>2.88</v>
+      </c>
+      <c r="AB12">
+        <v>2.48</v>
+      </c>
+      <c r="AC12">
+        <v>1.53</v>
+      </c>
+      <c r="AD12">
+        <v>4.5</v>
+      </c>
+      <c r="AE12">
         <v>1.18</v>
       </c>
-      <c r="V12">
-        <v>11.5</v>
-      </c>
-      <c r="W12">
-        <v>1.02</v>
-      </c>
-      <c r="X12">
-        <v>1.08</v>
-      </c>
-      <c r="Y12">
-        <v>5.65</v>
-      </c>
-      <c r="Z12">
-        <v>1.55</v>
-      </c>
-      <c r="AA12">
-        <v>2.2</v>
-      </c>
-      <c r="AB12">
-        <v>2.99</v>
-      </c>
-      <c r="AC12">
-        <v>1.34</v>
-      </c>
-      <c r="AD12">
-        <v>6</v>
-      </c>
-      <c r="AE12">
-        <v>1.11</v>
-      </c>
       <c r="AF12">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AG12">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="s">
         <v>92</v>
@@ -2059,7 +2059,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>50</v>
@@ -2086,73 +2086,73 @@
         <v>90</v>
       </c>
       <c r="L13">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="M13">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="N13">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="Q13">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="R13">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V13">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y13">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z13">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AA13">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AB13">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AC13">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AD13">
-        <v>4.65</v>
+        <v>5.99</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AH13">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AI13">
         <v>1.03</v>
@@ -2202,13 +2202,13 @@
         <v>90</v>
       </c>
       <c r="L14">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="N14">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="O14">
         <v>1.62</v>
@@ -2220,58 +2220,58 @@
         <v>3</v>
       </c>
       <c r="R14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S14">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="T14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U14">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V14">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y14">
-        <v>6.1</v>
+        <v>6.31</v>
       </c>
       <c r="Z14">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AA14">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AB14">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AC14">
         <v>1.38</v>
       </c>
       <c r="AD14">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AG14">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AH14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="s">
         <v>92</v>
@@ -2318,13 +2318,13 @@
         <v>90</v>
       </c>
       <c r="L15">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="M15">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="N15">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
         <v>1.91</v>
@@ -2336,55 +2336,55 @@
         <v>2.25</v>
       </c>
       <c r="R15">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
         <v>3.5</v>
       </c>
       <c r="U15">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V15">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="Z15">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AA15">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AB15">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AD15">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AE15">
         <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH15">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI15">
         <v>1</v>
@@ -2434,13 +2434,13 @@
         <v>90</v>
       </c>
       <c r="L16">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="M16">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N16">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O16">
         <v>1.73</v>
@@ -2452,43 +2452,43 @@
         <v>2.75</v>
       </c>
       <c r="R16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S16">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T16">
         <v>3.4</v>
       </c>
       <c r="U16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA16">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="AB16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AC16">
         <v>1.5</v>
       </c>
       <c r="AD16">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
@@ -2497,13 +2497,13 @@
         <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH16">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="AI16">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="s">
         <v>92</v>
@@ -2550,73 +2550,73 @@
         <v>90</v>
       </c>
       <c r="L17">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="M17">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N17">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="O17">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P17">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q17">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S17">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
         <v>6.5</v>
       </c>
       <c r="Z17">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA17">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB17">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AC17">
         <v>1.47</v>
       </c>
       <c r="AD17">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AG17">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH17">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="AI17">
         <v>1.05</v>
@@ -2666,13 +2666,13 @@
         <v>90</v>
       </c>
       <c r="L18">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="M18">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="N18">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O18">
         <v>1.67</v>
@@ -2684,58 +2684,58 @@
         <v>2.75</v>
       </c>
       <c r="R18">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T18">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V18">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>6.36</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AA18">
+        <v>2.4</v>
+      </c>
+      <c r="AB18">
         <v>2.55</v>
       </c>
-      <c r="AB18">
-        <v>2.37</v>
-      </c>
       <c r="AC18">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD18">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH18">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="AI18">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ18" t="s">
         <v>92</v>
@@ -2782,76 +2782,76 @@
         <v>90</v>
       </c>
       <c r="L19">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="M19">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="N19">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="P19">
         <v>6.75</v>
       </c>
       <c r="Q19">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S19">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="T19">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V19">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="Z19">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AA19">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AB19">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AC19">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD19">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
         <v>1.73</v>
       </c>
       <c r="AH19">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="AI19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ19" t="s">
         <v>92</v>
@@ -2898,76 +2898,76 @@
         <v>90</v>
       </c>
       <c r="L20">
-        <v>1.84</v>
+        <v>3.6</v>
       </c>
       <c r="M20">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N20">
-        <v>3.96</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S20">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T20">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V20">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y20">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z20">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AA20">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AB20">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AD20">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AH20">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="AI20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ20" t="s">
         <v>92</v>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -175,112 +175,112 @@
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Brann</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
     <t>Amazonas</t>
   </si>
   <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Bragantino</t>
   </si>
   <si>
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Shonan Bellmare</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
     <t>Salzburg</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
     <t>Palmeiras</t>
   </si>
   <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
     <t>Paysandu</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Internacional</t>
   </si>
   <si>
     <t>Flamengo</t>
@@ -926,76 +926,76 @@
         <v>90</v>
       </c>
       <c r="L3">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="M3">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="P3">
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
       <c r="Q3">
+        <v>2.6</v>
+      </c>
+      <c r="R3">
+        <v>1.34</v>
+      </c>
+      <c r="S3">
+        <v>2.95</v>
+      </c>
+      <c r="T3">
         <v>2.55</v>
       </c>
-      <c r="R3">
-        <v>1.43</v>
-      </c>
-      <c r="S3">
-        <v>2.6</v>
-      </c>
-      <c r="T3">
-        <v>2.95</v>
-      </c>
       <c r="U3">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V3">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AA3">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD3">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF3">
+        <v>1.78</v>
+      </c>
+      <c r="AG3">
         <v>1.9</v>
       </c>
-      <c r="AG3">
-        <v>1.78</v>
-      </c>
       <c r="AH3">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>92</v>
@@ -1042,76 +1042,76 @@
         <v>90</v>
       </c>
       <c r="L4">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="M4">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="P4">
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
       <c r="Q4">
+        <v>2.55</v>
+      </c>
+      <c r="R4">
+        <v>1.43</v>
+      </c>
+      <c r="S4">
         <v>2.6</v>
       </c>
-      <c r="R4">
-        <v>1.34</v>
-      </c>
-      <c r="S4">
+      <c r="T4">
         <v>2.95</v>
       </c>
-      <c r="T4">
-        <v>2.55</v>
-      </c>
       <c r="U4">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V4">
-        <v>6.25</v>
+        <v>7.75</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AA4">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AB4">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD4">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AE4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF4">
+        <v>1.9</v>
+      </c>
+      <c r="AG4">
         <v>1.78</v>
       </c>
-      <c r="AG4">
-        <v>1.9</v>
-      </c>
       <c r="AH4">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ4" t="s">
         <v>92</v>
@@ -1274,76 +1274,76 @@
         <v>91</v>
       </c>
       <c r="L6">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="M6">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AC6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AD6">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>92</v>
@@ -1390,13 +1390,13 @@
         <v>91</v>
       </c>
       <c r="L7">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="M7">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="N7">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1506,76 +1506,76 @@
         <v>91</v>
       </c>
       <c r="L8">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="M8">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB8">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="s">
         <v>92</v>
@@ -1827,7 +1827,7 @@
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -1854,76 +1854,76 @@
         <v>90</v>
       </c>
       <c r="L11">
-        <v>2.92</v>
+        <v>2.08</v>
       </c>
       <c r="M11">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="N11">
-        <v>2.31</v>
+        <v>3.74</v>
       </c>
       <c r="O11">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="R11">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="S11">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T11">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U11">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y11">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AA11">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="AB11">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AC11">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AD11">
-        <v>4.75</v>
+        <v>7.4</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AH11">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AI11">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ11" t="s">
         <v>92</v>
@@ -1943,7 +1943,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
@@ -1970,70 +1970,70 @@
         <v>90</v>
       </c>
       <c r="L12">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M12">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N12">
-        <v>3.06</v>
+        <v>3.87</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T12">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V12">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y12">
-        <v>7.27</v>
+        <v>6</v>
       </c>
       <c r="Z12">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA12">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB12">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="AC12">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AD12">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AE12">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH12">
         <v>10</v>
@@ -2059,7 +2059,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>50</v>
@@ -2086,37 +2086,37 @@
         <v>90</v>
       </c>
       <c r="L13">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="M13">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="N13">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="O13">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="R13">
         <v>1.57</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T13">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U13">
         <v>1.25</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>1.03</v>
@@ -2125,37 +2125,37 @@
         <v>1.11</v>
       </c>
       <c r="Y13">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="Z13">
+        <v>1.53</v>
+      </c>
+      <c r="AA13">
+        <v>2.38</v>
+      </c>
+      <c r="AB13">
+        <v>2.6</v>
+      </c>
+      <c r="AC13">
+        <v>1.43</v>
+      </c>
+      <c r="AD13">
+        <v>5</v>
+      </c>
+      <c r="AE13">
+        <v>1.13</v>
+      </c>
+      <c r="AF13">
+        <v>2.15</v>
+      </c>
+      <c r="AG13">
         <v>1.65</v>
       </c>
-      <c r="AA13">
-        <v>2.28</v>
-      </c>
-      <c r="AB13">
-        <v>2.8</v>
-      </c>
-      <c r="AC13">
-        <v>1.38</v>
-      </c>
-      <c r="AD13">
-        <v>5.99</v>
-      </c>
-      <c r="AE13">
-        <v>1.08</v>
-      </c>
-      <c r="AF13">
-        <v>2.42</v>
-      </c>
-      <c r="AG13">
-        <v>1.56</v>
-      </c>
       <c r="AH13">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="s">
         <v>92</v>
@@ -2175,7 +2175,7 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
@@ -2202,76 +2202,76 @@
         <v>90</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="M14">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="N14">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="O14">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P14">
+        <v>7</v>
+      </c>
+      <c r="Q14">
+        <v>2.4</v>
+      </c>
+      <c r="R14">
+        <v>1.5</v>
+      </c>
+      <c r="S14">
+        <v>2.4</v>
+      </c>
+      <c r="T14">
+        <v>3.4</v>
+      </c>
+      <c r="U14">
+        <v>1.29</v>
+      </c>
+      <c r="V14">
+        <v>8</v>
+      </c>
+      <c r="W14">
+        <v>1.03</v>
+      </c>
+      <c r="X14">
+        <v>1.08</v>
+      </c>
+      <c r="Y14">
         <v>6.5</v>
       </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
-      <c r="R14">
-        <v>1.57</v>
-      </c>
-      <c r="S14">
-        <v>2.3</v>
-      </c>
-      <c r="T14">
-        <v>3.8</v>
-      </c>
-      <c r="U14">
-        <v>1.24</v>
-      </c>
-      <c r="V14">
-        <v>13</v>
-      </c>
-      <c r="W14">
-        <v>1.04</v>
-      </c>
-      <c r="X14">
-        <v>1.1</v>
-      </c>
-      <c r="Y14">
-        <v>6.31</v>
-      </c>
       <c r="Z14">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AA14">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AB14">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC14">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="AG14">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AH14">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AI14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ14" t="s">
         <v>92</v>
@@ -2318,13 +2318,13 @@
         <v>90</v>
       </c>
       <c r="L15">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="M15">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="O15">
         <v>1.91</v>
@@ -2336,19 +2336,19 @@
         <v>2.25</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V15">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2357,31 +2357,31 @@
         <v>1.11</v>
       </c>
       <c r="Y15">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AA15">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AB15">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC15">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AD15">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH15">
         <v>9.199999999999999</v>
@@ -2434,13 +2434,13 @@
         <v>90</v>
       </c>
       <c r="L16">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="M16">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N16">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="O16">
         <v>1.73</v>
@@ -2452,7 +2452,7 @@
         <v>2.75</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S16">
         <v>2.38</v>
@@ -2467,25 +2467,25 @@
         <v>8.5</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA16">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="AB16">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AC16">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AD16">
         <v>4.75</v>
@@ -2497,7 +2497,7 @@
         <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH16">
         <v>11.5</v>
@@ -2550,28 +2550,28 @@
         <v>90</v>
       </c>
       <c r="L17">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="M17">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="N17">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="O17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P17">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q17">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S17">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T17">
         <v>3.3</v>
@@ -2580,46 +2580,46 @@
         <v>1.29</v>
       </c>
       <c r="V17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z17">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA17">
         <v>2.55</v>
       </c>
       <c r="AB17">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AC17">
         <v>1.47</v>
       </c>
       <c r="AD17">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AE17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH17">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ17" t="s">
         <v>92</v>
@@ -2666,13 +2666,13 @@
         <v>90</v>
       </c>
       <c r="L18">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M18">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N18">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O18">
         <v>1.67</v>
@@ -2687,55 +2687,55 @@
         <v>1.5</v>
       </c>
       <c r="S18">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V18">
         <v>8.5</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y18">
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AA18">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB18">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AC18">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
         <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AH18">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI18">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ18" t="s">
         <v>92</v>
@@ -2782,76 +2782,76 @@
         <v>90</v>
       </c>
       <c r="L19">
-        <v>2.55</v>
+        <v>1.84</v>
       </c>
       <c r="M19">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="O19">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P19">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S19">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U19">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>7.17</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AA19">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AB19">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AC19">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AD19">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE19">
         <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG19">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AH19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ19" t="s">
         <v>92</v>
@@ -2898,13 +2898,13 @@
         <v>90</v>
       </c>
       <c r="L20">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="M20">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="O20">
         <v>2.38</v>
@@ -2919,40 +2919,40 @@
         <v>1.5</v>
       </c>
       <c r="S20">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="U20">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AA20">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AC20">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AD20">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE20">
         <v>1.2</v>
@@ -2961,13 +2961,13 @@
         <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH20">
         <v>8.5</v>
       </c>
       <c r="AI20">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ20" t="s">
         <v>92</v>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,111 +648,111 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="M2" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="P2" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>7.75</v>
+        <v>8.6</v>
       </c>
       <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.07</v>
       </c>
-      <c r="X2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '45+4', '71', '90+4']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -789,20 +789,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -879,12 +879,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '64', '90+4']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '59']</t>
         </is>
       </c>
       <c r="AL3" s="3" t="n">
@@ -921,20 +921,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '90+4']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,106 +1044,106 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="P5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH5" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AI5" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '43']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.89</v>
+        <v>1.71</v>
       </c>
       <c r="M6" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="N6" t="n">
-        <v>2.51</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.71</v>
+        <v>2.51</v>
       </c>
       <c r="M7" t="n">
-        <v>3.58</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="O8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="T11" t="n">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.75</v>
+        <v>5.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.87</v>
+        <v>4.24</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P12" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
         <v>12</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>2.46</v>
       </c>
       <c r="M13" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="N13" t="n">
-        <v>3.53</v>
+        <v>3.73</v>
       </c>
       <c r="O13" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.4</v>
       </c>
-      <c r="R13" t="n">
+      <c r="AG13" t="n">
         <v>1.53</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH13" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
         <v>2.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AD14" t="n">
         <v>5.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>1.91</v>
@@ -2408,52 +2408,52 @@
         <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
         <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.15</v>
+        <v>5.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="n">
         <v>13</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,73 +2522,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="N16" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
         <v>6.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.25</v>
+        <v>6.03</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>1.02</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,43 +2654,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.96</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
         <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
         <v>6</v>
@@ -2702,25 +2702,25 @@
         <v>2.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
         <v>1.02</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="M18" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.53</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
         <v>2.38</v>
@@ -2936,7 +2936,7 @@
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
         <v>2.4</v>
@@ -2948,7 +2948,7 @@
         <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
         <v>1.04</v>
@@ -2966,22 +2966,22 @@
         <v>2.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AE19" t="n">
         <v>1.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
         <v>8.5</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.67</v>
       </c>
       <c r="P20" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y20" t="n">
         <v>6.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,25 +648,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH2" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AI2" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>['33', '45+4', '71', '90+4']</t>
+          <t>['38', '64', '90+4']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['45+1', '59']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,111 +780,111 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
+      <c r="R3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="AG3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH3" t="n">
         <v>8</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>1.07</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>['38', '64', '90+4']</t>
+          <t>['33', '45+4', '71', '90+4']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>['45+1', '59']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AL3" s="3" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.51</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="O17" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.3</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="P19" t="n">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.4</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,111 +648,111 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="AG2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH2" t="n">
         <v>8</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>1.07</v>
       </c>
-      <c r="X2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>['38', '64', '90+4']</t>
+          <t>['33', '45+4', '71', '90+4']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>['45+1', '59']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,25 +780,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -806,85 +806,85 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH3" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AI3" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>['33', '45+4', '71', '90+4']</t>
+          <t>['38', '64', '90+4']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['45+1', '59']</t>
         </is>
       </c>
       <c r="AL3" s="3" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.71</v>
+        <v>2.51</v>
       </c>
       <c r="M6" t="n">
-        <v>3.58</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.51</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>3.73</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>3.82</v>
+        <v>4.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.24</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.57</v>
@@ -2018,25 +2018,25 @@
         <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
         <v>2.4</v>
@@ -2045,7 +2045,7 @@
         <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
         <v>5.5</v>
@@ -2054,10 +2054,10 @@
         <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="n">
         <v>12</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.73</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="T13" t="n">
-        <v>4.45</v>
+        <v>3.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.1</v>
+        <v>5.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>4.24</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.57</v>
@@ -2282,25 +2282,25 @@
         <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
         <v>2.4</v>
@@ -2309,7 +2309,7 @@
         <v>2.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AD14" t="n">
         <v>5.5</v>
@@ -2318,10 +2318,10 @@
         <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="n">
         <v>12</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
         <v>6.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
         <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>1.98</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
         <v>6.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
         <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -638,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,114 +643,111 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.45</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y2" t="n">
-        <v>7.5</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.01</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['45', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>1.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['33', '45+4', '71', '90+4']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45861.3125</v>
       </c>
     </row>
@@ -770,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,114 +772,111 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['33', '45+4', '71', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['38', '64', '90+4']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>['45+1', '59']</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AK3" s="3" t="n">
         <v>45861.3125</v>
       </c>
     </row>
@@ -912,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -938,88 +927,85 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>9.75</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.6</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>2.95</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['39', '43']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.55</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>['45', '90+4']</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AK4" s="3" t="n">
         <v>45861.3125</v>
       </c>
     </row>
@@ -1044,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1070,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.77</v>
+        <v>3.87</v>
       </c>
       <c r="M5" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>1.68</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>7.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1097,61 +1083,58 @@
         <v>2.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V5" t="n">
-        <v>7.75</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>1.93</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.9</v>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['38', '64', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['45+1', '59']</t>
+        </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>7.5</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>['39', '43']</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45861.3125</v>
       </c>
     </row>
@@ -1176,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,88 +1185,85 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.51</v>
+        <v>1.71</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.5</v>
+        <v>2.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45861.5</v>
       </c>
     </row>
@@ -1308,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,88 +1314,85 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="M7" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45861.5</v>
       </c>
     </row>
@@ -1440,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>2.89</v>
       </c>
       <c r="M8" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.51</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1505,28 +1482,32 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1537,17 +1518,10 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45861.5</v>
       </c>
     </row>
@@ -1581,20 +1555,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1607,13 +1581,13 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -1628,58 +1602,55 @@
         <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>1.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['58', '61', '87', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45861.58333333334</v>
       </c>
     </row>
@@ -1716,17 +1687,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1739,13 +1710,13 @@
         <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>2.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -1760,58 +1731,55 @@
         <v>1.46</v>
       </c>
       <c r="V10" t="n">
-        <v>6.15</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>1.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['12', '81', '85']</t>
+        </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.15</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45861.65625</v>
       </c>
     </row>
@@ -1845,105 +1813,102 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="N11" t="n">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.82</v>
+        <v>3.26</v>
       </c>
       <c r="P11" t="n">
-        <v>5.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
         <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X11" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.14</v>
+        <v>6.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45861.79166666666</v>
       </c>
     </row>
@@ -1977,105 +1942,102 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="O12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['11', '40', '36', '72']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['16', '80']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.62</v>
       </c>
-      <c r="P12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="AJ12" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AK12" s="3" t="n">
         <v>45861.79166666666</v>
       </c>
     </row>
@@ -2100,114 +2062,111 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>4.86</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.82</v>
+        <v>3.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.65</v>
+        <v>2.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.8</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['16', '22']</t>
+        </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>1.78</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45861.79166666666</v>
       </c>
     </row>
@@ -2232,48 +2191,48 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.24</v>
+        <v>2.49</v>
       </c>
       <c r="O14" t="n">
-        <v>1.73</v>
+        <v>3.53</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
         <v>1.57</v>
@@ -2282,64 +2241,61 @@
         <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['45+4', '62']</t>
+        </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>12</v>
+        <v>1.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45861.79166666666</v>
       </c>
     </row>
@@ -2386,92 +2342,89 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="O15" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="T15" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="U15" t="n">
         <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45861.8125</v>
       </c>
     </row>
@@ -2486,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,114 +2449,111 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="N16" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.58</v>
       </c>
       <c r="U16" t="n">
         <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>2.37</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45861.89583333334</v>
       </c>
     </row>
@@ -2618,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,114 +2578,111 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.55</v>
       </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="Y17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['85', '50', '45+6']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.67</v>
       </c>
-      <c r="P17" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V17" t="n">
-        <v>10</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AJ17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK17" s="3" t="n">
         <v>45861.89583333334</v>
       </c>
     </row>
@@ -2760,114 +2707,111 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="N18" t="n">
-        <v>1.98</v>
+        <v>3.32</v>
       </c>
       <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.38</v>
       </c>
-      <c r="P18" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>2.55</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.62</v>
+        <v>4.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['9', '75']</t>
+        </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AH18" t="n">
-        <v>8.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45861.89583333334</v>
       </c>
     </row>
@@ -2882,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,19 +2836,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2914,92 +2858,89 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="M19" t="n">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="P19" t="n">
-        <v>5.75</v>
+        <v>2.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.55</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.44</v>
+        <v>1.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['66', '85']</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45861.89583333334</v>
       </c>
     </row>
@@ -3014,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -3046,92 +2987,89 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.67</v>
-      </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
         <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.25</v>
+        <v>2.65</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.55</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['90+4', '54']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['90+9', '89']</t>
+        </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45861.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-23.xlsx
+++ b/jogos_2025-07-23.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="M2" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA2" t="n">
         <v>4.2</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['33', '45+4', '71', '90+4']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['45', '90+4']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45861.3125</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="P3" t="n">
         <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['33', '45+4', '71', '90+4']</t>
+          <t>['38', '64', '90+4']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['45+1', '59']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.05</v>
+        <v>1.23</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45861.3125</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
         <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['45', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['39', '43']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45861.3125</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.87</v>
+        <v>1.77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1083,7 +1083,7 @@
         <v>2.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
@@ -1095,10 +1095,10 @@
         <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA5" t="n">
         <v>3.8</v>
@@ -1107,32 +1107,32 @@
         <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['38', '64', '90+4']</t>
+          <t>['39', '43']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['45+1', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45861.3125</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.51</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45861.5</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45861.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
-        <v>3.26</v>
+        <v>3.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '62']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45861.79166666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="N12" t="n">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T12" t="n">
         <v>4.2</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.5</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['11', '40', '36', '72']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['16', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45861.79166666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2.49</v>
+        <v>3.87</v>
       </c>
       <c r="O14" t="n">
-        <v>3.53</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['11', '40', '36', '72']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['45+4', '62']</t>
+          <t>['16', '80']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45861.79166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="M16" t="n">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.53</v>
+        <v>3.32</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Z16" t="n">
         <v>1.47</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['9', '75']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45861.89583333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,78 +2578,78 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.93</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AB17" t="n">
         <v>1.17</v>
@@ -2658,29 +2658,29 @@
         <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['85', '50', '45+6']</t>
+          <t>['90+4', '54']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['90+9', '89']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45861.89583333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="M18" t="n">
-        <v>3.09</v>
+        <v>2.84</v>
       </c>
       <c r="N18" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>4.29</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Z18" t="n">
         <v>1.47</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['9', '75']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45861.89583333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="M20" t="n">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="N20" t="n">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X20" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="AB20" t="n">
         <v>1.17</v>
@@ -3045,29 +3045,29 @@
         <v>2.2</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['85', '50', '45+6']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.65</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['90+4', '54']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['90+9', '89']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45861.89583333334</v>
